--- a/signup_forms/007_signup_form--signup_forms.xlsx
+++ b/signup_forms/007_signup_form--signup_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_at_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>created at</t>
+          <t>Created At 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_at_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>updated at</t>
+          <t>Updated At 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>created_by_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>created by</t>
+          <t>Created By 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1222,7 +1222,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>created_by_choices</t>
+          <t>created_by_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>created_by_choices</t>
+          <t>created_by_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>created_by_choices</t>
+          <t>created_by_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
